--- a/docs/sample-two-row.xlsx
+++ b/docs/sample-two-row.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Benefit</t>
   </si>
@@ -26,12 +26,6 @@
   </si>
   <si>
     <t>Premium</t>
-  </si>
-  <si>
-    <t>Group A</t>
-  </si>
-  <si>
-    <t>Group B</t>
   </si>
   <si>
     <t>Doctor Visits</t>
@@ -450,58 +444,48 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
